--- a/Books/TravelBooksExport.xlsx
+++ b/Books/TravelBooksExport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aidancarter/Desktop/CodexSandbox/Website/Books/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD01EAC5-2B21-9D4D-9F7F-8F86DD369A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D3D874-217B-0440-9F0E-4D2910330F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="262">
   <si>
     <t>Title</t>
   </si>
@@ -783,6 +783,42 @@
   </si>
   <si>
     <t>Ireland</t>
+  </si>
+  <si>
+    <t>Mayan World</t>
+  </si>
+  <si>
+    <t>The Code of Kings: The Language of Seven Sacred Maya Temples and Tombs</t>
+  </si>
+  <si>
+    <t>Breaking the Maya Code</t>
+  </si>
+  <si>
+    <t>The Maya</t>
+  </si>
+  <si>
+    <t>Schele, Linda</t>
+  </si>
+  <si>
+    <t>Coe, Michael D.</t>
+  </si>
+  <si>
+    <t>[0684852098]</t>
+  </si>
+  <si>
+    <t>[0684852098, 9780684852096]</t>
+  </si>
+  <si>
+    <t>[0500289557]</t>
+  </si>
+  <si>
+    <t>[0500289557, 9780500289556]</t>
+  </si>
+  <si>
+    <t>[0500277168]</t>
+  </si>
+  <si>
+    <t>[0500277168, 9780500277164]</t>
   </si>
 </sst>
 </file>
@@ -832,15 +868,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1145,12 +1180,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.83203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="29.83203125" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" style="7" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="255.83203125" bestFit="1" customWidth="1"/>
@@ -1158,13 +1193,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>235</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1202,13 +1237,13 @@
       <c r="X1" s="1"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>239</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1246,13 +1281,13 @@
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1290,13 +1325,13 @@
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>238</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1334,13 +1369,13 @@
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>237</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -1378,13 +1413,13 @@
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>241</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -1420,13 +1455,13 @@
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>237</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -1464,13 +1499,13 @@
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>242</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -1508,13 +1543,13 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>243</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -1550,13 +1585,13 @@
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>243</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -1592,13 +1627,13 @@
       <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>243</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -1634,13 +1669,13 @@
       <c r="X11" s="3"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>244</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>83</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -1676,13 +1711,13 @@
       <c r="X12" s="3"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>90</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -1718,13 +1753,13 @@
       <c r="X13" s="3"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>238</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -1762,13 +1797,13 @@
       <c r="X14" s="3"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -1804,13 +1839,13 @@
       <c r="X15" s="3"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -1842,13 +1877,13 @@
       <c r="X16" s="3"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>245</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -1884,13 +1919,13 @@
       <c r="X17" s="3"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>236</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -1928,13 +1963,13 @@
       <c r="X18" s="3"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>245</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>132</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -1970,13 +2005,13 @@
       <c r="X19" s="3"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>246</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -2008,13 +2043,13 @@
       <c r="X20" s="3"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>247</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -2050,13 +2085,13 @@
       <c r="X21" s="3"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>244</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2092,13 +2127,13 @@
       <c r="X22" s="3"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>248</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -2136,13 +2171,13 @@
       <c r="X23" s="3"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>248</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -2180,13 +2215,13 @@
       <c r="X24" s="3"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>243</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -2222,13 +2257,13 @@
       <c r="X25" s="3"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>249</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -2264,13 +2299,13 @@
       <c r="X26" s="3"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>247</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>183</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -2308,13 +2343,13 @@
       <c r="X27" s="3"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>249</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>191</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -2350,13 +2385,13 @@
       <c r="X28" s="3"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>248</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>197</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -2392,13 +2427,13 @@
       <c r="X29" s="3"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>236</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>203</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -2436,13 +2471,13 @@
       <c r="X30" s="3"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>239</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>208</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -2478,13 +2513,13 @@
       <c r="X31" s="3"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>236</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>214</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -2520,13 +2555,13 @@
       <c r="X32" s="3"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>237</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>220</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -2564,13 +2599,13 @@
       <c r="X33" s="3"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>238</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>226</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -2606,13 +2641,13 @@
       <c r="X34" s="3"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>238</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -2648,13 +2683,13 @@
       <c r="X35" s="3"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>231</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -2689,6 +2724,75 @@
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
     </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
